--- a/Analysis 2024.xlsx
+++ b/Analysis 2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,60 +501,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Rank_Spearman_Rating_Stat</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Spearman_Rating_PValue</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Rank_Kendall_Stat</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Rank_Kendall_PValue</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Kendall_Rating_Stat</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_Kendall_Rating_PValue</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Top_5_5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Top_5_25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Top_10_10</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Top_10_50</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Top_20_20</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Top_20_50</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Top_5_5 (rating)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Top_5_25 (rating)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Top_10_10 (rating)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Top_10_50 (rating)</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Top_20_20 (rating)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Top_20_50 (rating)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>TruePositives</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>FalsePositives</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>FalseNegatives</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>TrueNegatives</t>
         </is>
@@ -609,39 +659,69 @@
         <v>0.03657545127951591</v>
       </c>
       <c r="P2" t="n">
+        <v>0.1975510204081632</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.04999510046539519</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.1453308596165739</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.03306357428090639</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="U2" t="n">
+        <v>0.05413719039015746</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>5</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>5</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
         <v>10</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="n">
         <v>30</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>69</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,39 +774,69 @@
         <v>0.005860829327448052</v>
       </c>
       <c r="P3" t="n">
+        <v>0.2461719233147804</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.01404165391953542</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.1882086167800454</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.00577796704721702</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.1700680272108843</v>
       </c>
       <c r="U3" t="n">
+        <v>0.01262816937962632</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
         <v>8</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
         <v>5</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>12</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
         <v>30</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>69</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AK3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -779,39 +889,69 @@
         <v>0.003866287783835871</v>
       </c>
       <c r="P4" t="n">
+        <v>0.1905590727387487</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.06017680797683008</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.2026088786029876</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.003119242002503862</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>0.1314958973280034</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.05507140987077751</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
         <v>5</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
         <v>5</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>12</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH4" t="n">
         <v>30</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>68</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AK4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -864,39 +1004,69 @@
         <v>0.1675711083905241</v>
       </c>
       <c r="P5" t="n">
+        <v>0.1573597359735974</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1179182071673789</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.08888888888888891</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.1900702284813363</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.1034343434343434</v>
       </c>
       <c r="U5" t="n">
+        <v>0.1273100390036617</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
         <v>4</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Z5" t="n">
         <v>5</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>11</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
         <v>30</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>70</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AK5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -949,39 +1119,69 @@
         <v>0.01077340150938644</v>
       </c>
       <c r="P6" t="n">
+        <v>0.2375517551755175</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0173209098000836</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.1656565656565657</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.01460389056252366</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.162020202020202</v>
       </c>
       <c r="U6" t="n">
+        <v>0.01691962592007781</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>8</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
         <v>3</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
         <v>15</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
         <v>30</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>70</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AK6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,39 +1234,69 @@
         <v>0.01642795592690669</v>
       </c>
       <c r="P7" t="n">
+        <v>0.1686288628862886</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0935188707194558</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.162020202020202</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.01691962592007781</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.1078787878787879</v>
       </c>
       <c r="U7" t="n">
+        <v>0.1117639623197127</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>7</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
         <v>5</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
         <v>13</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
         <v>30</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>70</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AK7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1119,39 +1349,69 @@
         <v>0.004797397213034688</v>
       </c>
       <c r="P8" t="n">
+        <v>0.2608460846084608</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.008761820428228448</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.1987878787878788</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.003384530279201218</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>0.1793939393939394</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.00817953406214531</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>4</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
         <v>8</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
         <v>8</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
         <v>13</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
         <v>30</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>70</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AK8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1204,39 +1464,69 @@
         <v>0.02536007544586125</v>
       </c>
       <c r="P9" t="n">
+        <v>0.2317196794369107</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02168632086872147</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.1458026509572901</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.03341802270997973</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1512728802861351</v>
       </c>
       <c r="U9" t="n">
+        <v>0.0273261762437398</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>7</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
         <v>2</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AA9" t="n">
         <v>11</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH9" t="n">
         <v>29</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>69</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AK9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1289,39 +1579,69 @@
         <v>0.1037076364921666</v>
       </c>
       <c r="P10" t="n">
+        <v>0.1950675067506751</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.05178980310213879</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.1046464646464647</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.1229122004709293</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>0.1357575757575758</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04536066412945635</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>5</v>
       </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>9</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
         <v>30</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>70</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1374,39 +1694,69 @@
         <v>0.2741446659607767</v>
       </c>
       <c r="P11" t="n">
+        <v>0.1863662284419647</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.07528240989071673</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.0716674629718108</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.3116143924036124</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.1275680840898232</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0.07169092904650362</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>3</v>
       </c>
       <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>65</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AK11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1459,39 +1809,69 @@
         <v>0.6234534766624957</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.02984399007963072</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7705047395436078</v>
+      </c>
+      <c r="R12" t="n">
         <v>-0.03387334315169366</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.6211951097625377</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.01493793393646118</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.8274912181413644</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>5</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH12" t="n">
         <v>29</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>69</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AK12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1544,39 +1924,69 @@
         <v>0.09236442933394763</v>
       </c>
       <c r="P13" t="n">
+        <v>0.04673267326732673</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6442938399286017</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.1143434343434344</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.09187015128185612</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
+        <v>0.0395959595959596</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5594148390405405</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
         <v>8</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Z13" t="n">
         <v>4</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>12</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>30</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>70</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AK13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1629,39 +2039,69 @@
         <v>0.9241326712262308</v>
       </c>
       <c r="P14" t="n">
+        <v>0.0150976668475312</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8839238658694011</v>
+      </c>
+      <c r="R14" t="n">
         <v>-0.004824561403508771</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.9444840737693221</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.01052631578947368</v>
       </c>
       <c r="U14" t="n">
+        <v>0.8792412027606161</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>5</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Z14" t="n">
         <v>4</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
         <v>9</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH14" t="n">
         <v>28</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AI14" t="n">
         <v>2</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AJ14" t="n">
         <v>68</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AK14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1714,39 +2154,69 @@
         <v>0.5613716407226839</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.02829931972789116</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.7809706727354258</v>
+      </c>
+      <c r="R15" t="n">
         <v>-0.04267161410018553</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.5314533298646478</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.02123273551844981</v>
       </c>
       <c r="U15" t="n">
+        <v>0.7555095170785102</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>5</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Z15" t="n">
         <v>3</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AA15" t="n">
         <v>9</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH15" t="n">
         <v>30</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>69</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AK15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1799,39 +2269,69 @@
         <v>0.7443237799106217</v>
       </c>
       <c r="P16" t="n">
+        <v>0.0473130208034479</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6436333959090293</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.01872501577950768</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.7847243176322019</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.02503681885125184</v>
       </c>
       <c r="U16" t="n">
+        <v>0.7149272740100578</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>5</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Z16" t="n">
         <v>3</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AA16" t="n">
         <v>11</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
         <v>11</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AI16" t="n">
         <v>19</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AJ16" t="n">
         <v>25</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AK16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1884,39 +2384,69 @@
         <v>0.8674033553536538</v>
       </c>
       <c r="P17" t="n">
+        <v>0.02712760361876709</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7919641868868109</v>
+      </c>
+      <c r="R17" t="n">
         <v>-0.001718213058419244</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.9801082366692063</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0.01073883161512028</v>
       </c>
       <c r="U17" t="n">
+        <v>0.8761649965497997</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>5</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Z17" t="n">
         <v>2</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
         <v>8</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
         <v>14</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AI17" t="n">
         <v>16</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AJ17" t="n">
         <v>30</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AK17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1969,39 +2499,69 @@
         <v>0.06300893005894717</v>
       </c>
       <c r="P18" t="n">
+        <v>0.1655534941249227</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1014972663476953</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.1292517006802721</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.05802541157463768</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
+        <v>0.1078128220985364</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1138552174895955</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
         <v>7</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
         <v>11</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AI18" t="n">
         <v>15</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AJ18" t="n">
         <v>28</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AK18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2054,39 +2614,69 @@
         <v>0.2168186582063196</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.1133818589025756</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2739496179608055</v>
+      </c>
+      <c r="R19" t="n">
         <v>-0.08398656215005598</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.2279490076588873</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>-0.07502799552071668</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2814555364312193</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>4</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
         <v>3</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
         <v>8</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
         <v>14</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AI19" t="n">
         <v>16</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AJ19" t="n">
         <v>30</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AK19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Analysis 2024.xlsx
+++ b/Analysis 2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2226,80 +2226,80 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024 Llama-Abstract-100</t>
+          <t>2024 Llama-Full Text-Zeroshot</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7857142857142857</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7959183673469388</v>
+        <v>2.540816326530612</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7040816326530612</v>
+        <v>3.510204081632653</v>
       </c>
       <c r="F16" t="n">
-        <v>4.989795918367347</v>
+        <v>17.69387755102041</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8673469387755102</v>
+        <v>2.020408163265306</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8543137311935425</v>
+        <v>0.8486763834953308</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8728998899459839</v>
+        <v>0.8676711320877075</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8632783889770508</v>
+        <v>0.8578673601150513</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8222048878669739</v>
+        <v>0.8054565191268921</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8450055718421936</v>
+        <v>0.8533537983894348</v>
       </c>
       <c r="M16" t="n">
-        <v>0.83311927318573</v>
+        <v>0.8284876346588135</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03336329845902747</v>
+        <v>0.1730135353110316</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7443237799106217</v>
+        <v>0.08844757172115031</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0473130208034479</v>
+        <v>0.1295832297305051</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6436333959090293</v>
+        <v>0.2034730397228623</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01872501577950768</v>
+        <v>0.1138228487271197</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7847243176322019</v>
+        <v>0.09681567243733653</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02503681885125184</v>
+        <v>0.09025878392594151</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7149272740100578</v>
+        <v>0.1879292653960486</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
         <v>11</v>
@@ -2308,28 +2308,28 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF16" t="n">
         <v>5</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2341,71 +2341,71 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024 Llama-Summary-100</t>
+          <t>2024 Llama-Full Text-Oneshot</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8556701030927835</v>
+        <v>2.210526315789474</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8762886597938144</v>
+        <v>2.452631578947368</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6288659793814433</v>
+        <v>2.852631578947368</v>
       </c>
       <c r="F17" t="n">
-        <v>5.608247422680412</v>
+        <v>15.11578947368421</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7938144329896907</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8523997664451599</v>
+        <v>0.8651831150054932</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8712306022644043</v>
+        <v>0.8633482456207275</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8614739179611206</v>
+        <v>0.8640860319137573</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8189289569854736</v>
+        <v>0.8195154070854187</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8478923439979553</v>
+        <v>0.8589154481887817</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8327944874763489</v>
+        <v>0.8385164141654968</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01717336419103724</v>
+        <v>0.2345464725643897</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8674033553536538</v>
+        <v>0.02214767084202533</v>
       </c>
       <c r="P17" t="n">
-        <v>0.02712760361876709</v>
+        <v>0.2674692049272117</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.7919641868868109</v>
+        <v>0.008783162769266344</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.001718213058419244</v>
+        <v>0.1583426651735722</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9801082366692063</v>
+        <v>0.0230220183814985</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01073883161512028</v>
+        <v>0.1843225083986562</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8761649965497997</v>
+        <v>0.00814451034238459</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -2414,37 +2414,37 @@
         <v>5</v>
       </c>
       <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2</v>
       </c>
-      <c r="AA17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2456,80 +2456,80 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024 Llama-Abstract-1000</t>
+          <t>2024 Llama-Abstract-100</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7373737373737373</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="E18" t="n">
-        <v>0.494949494949495</v>
+        <v>0.7040816326530612</v>
       </c>
       <c r="F18" t="n">
-        <v>4.070707070707071</v>
+        <v>4.989795918367347</v>
       </c>
       <c r="G18" t="n">
-        <v>1.01010101010101</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8563129305839539</v>
+        <v>0.8543137311935425</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8746190667152405</v>
+        <v>0.8728998899459839</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8651073575019836</v>
+        <v>0.8632783889770508</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8235912919044495</v>
+        <v>0.8222048878669739</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8461512327194214</v>
+        <v>0.8450055718421936</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8344148397445679</v>
+        <v>0.83311927318573</v>
       </c>
       <c r="N18" t="n">
-        <v>0.187569573283859</v>
+        <v>0.03336329845902747</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06300893005894717</v>
+        <v>0.7443237799106217</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1655534941249227</v>
+        <v>0.0473130208034479</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1014972663476953</v>
+        <v>0.6436333959090293</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1292517006802721</v>
+        <v>0.01872501577950768</v>
       </c>
       <c r="S18" t="n">
-        <v>0.05802541157463768</v>
+        <v>0.7847243176322019</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1078128220985364</v>
+        <v>0.02503681885125184</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1138552174895955</v>
+        <v>0.7149272740100578</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
         <v>11</v>
@@ -2541,25 +2541,25 @@
         <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -2571,101 +2571,101 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024 Llama Time Finetuned</t>
+          <t>2024 Llama-Summary-100</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.6288659793814433</v>
       </c>
       <c r="F19" t="n">
-        <v>5.684210526315789</v>
+        <v>5.608247422680412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7578947368421053</v>
+        <v>0.7938144329896907</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8563008308410645</v>
+        <v>0.8523997664451599</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8734758496284485</v>
+        <v>0.8712306022644043</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8645732402801514</v>
+        <v>0.8614739179611206</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8225367069244385</v>
+        <v>0.8189289569854736</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8492844104766846</v>
+        <v>0.8478923439979553</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8354087471961975</v>
+        <v>0.8327944874763489</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1278835386338186</v>
+        <v>-0.01717336419103724</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2168186582063196</v>
+        <v>0.8674033553536538</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1133818589025756</v>
+        <v>0.02712760361876709</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2739496179608055</v>
+        <v>0.7919641868868109</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.08398656215005598</v>
+        <v>-0.001718213058419244</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2279490076588873</v>
+        <v>0.9801082366692063</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07502799552071668</v>
+        <v>0.01073883161512028</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2814555364312193</v>
+        <v>0.8761649965497997</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3</v>
       </c>
       <c r="AA19" t="n">
         <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF19" t="n">
         <v>5</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>14</v>
@@ -2677,6 +2677,236 @@
         <v>30</v>
       </c>
       <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024 Llama-Abstract-1000</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7373737373737373</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.494949494949495</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.070707070707071</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.01010101010101</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8563129305839539</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8746190667152405</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8651073575019836</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8235912919044495</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8461512327194214</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8344148397445679</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.187569573283859</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06300893005894717</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1655534941249227</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1014972663476953</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1292517006802721</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.05802541157463768</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1078128220985364</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1138552174895955</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024 Llama Time Finetuned</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7473684210526316</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8631578947368421</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.684210526315789</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7578947368421053</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8563008308410645</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8734758496284485</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8645732402801514</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8225367069244385</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8492844104766846</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8354087471961975</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.1278835386338186</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2168186582063196</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1133818589025756</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2739496179608055</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.08398656215005598</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2279490076588873</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.07502799552071668</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2814555364312193</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK21" t="n">
         <v>0</v>
       </c>
     </row>
